--- a/laporan_padel_dki_jakarta_2026-10-12.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-12.xlsx
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp8.550.500</t>
+          <t>Rp8.275.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>34</v>
       </c>
       <c r="D38" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp2.680.000</t>
+          <t>Rp2.868.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.050.000</t>
+          <t>Rp1.340.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-12.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-12.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp640.000</t>
+          <t>Rp720.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp8.275.500</t>
+          <t>Rp8.550.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.170.000</t>
+          <t>Rp2.890.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp5.150.000</t>
+          <t>Rp5.950.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp1.875.000</t>
+          <t>Rp2.250.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp765.000</t>
+          <t>Rp665.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>85</v>
       </c>
       <c r="D33" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp2.094.000</t>
+          <t>Rp1.494.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp750.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1908,16 +1908,16 @@
         <v>105</v>
       </c>
       <c r="D48" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp5.550.000</t>
+          <t>Rp5.725.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2001,16 +2001,16 @@
         <v>64</v>
       </c>
       <c r="D51" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp1.728.000</t>
+          <t>Rp2.304.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>32</v>
       </c>
       <c r="D58" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.125.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>90</v>
       </c>
       <c r="D61" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp7.920.000</t>
+          <t>Rp8.360.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>102</v>
       </c>
       <c r="D70" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp7.575.000</t>
+          <t>Rp6.975.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>126</v>
       </c>
       <c r="D80" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp2.684.000</t>
+          <t>Rp2.982.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp5.500.000</t>
+          <t>Rp5.450.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>127</v>
       </c>
       <c r="D3" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp15.111.500</t>
+          <t>Rp15.246.500</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3788,16 +3788,16 @@
         <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.225.000</t>
+          <t>Rp2.325.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3819,16 +3819,16 @@
         <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp700.000</t>
+          <t>Rp875.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp500.000</t>
+          <t>Rp300.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>159</v>
       </c>
       <c r="D37" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp12.800.000</t>
+          <t>Rp13.100.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp5.050.000</t>
+          <t>Rp5.300.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5679,16 +5679,16 @@
         <v>30</v>
       </c>
       <c r="D70" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp1.750.000</t>
+          <t>Rp1.875.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5916,16 +5916,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp800.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp18.250.000</t>
+          <t>Rp19.450.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.900.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp624.000</t>
+          <t>Rp984.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.900.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6381,16 +6381,16 @@
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp336.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6441,7 +6441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7083,16 +7083,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp18.100.000</t>
+          <t>Rp19.300.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp5.900.000</t>
+          <t>Rp6.150.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>96</v>
       </c>
       <c r="D31" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.450.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>108</v>
       </c>
       <c r="D33" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp6.550.000</t>
+          <t>Rp6.940.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>187</v>
       </c>
       <c r="D34" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp10.150.000</t>
+          <t>Rp10.350.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>34</v>
       </c>
       <c r="D38" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp2.868.000</t>
+          <t>Rp3.244.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>150</v>
       </c>
       <c r="D40" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp22.475.000</t>
+          <t>Rp22.825.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7944,28 +7944,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Let's Go Padel Sunter</t>
+          <t>House of Mayor</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D49" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp8.080.000</t>
+          <t>Rp5.093.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp350.000</t>
+          <t>Rp229.000 - Rp349.000</t>
         </is>
       </c>
     </row>
@@ -7975,28 +7975,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Padre Padel Kelapa Gading</t>
+          <t>Let's Go Padel Sunter</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>144</v>
+        <v>98</v>
       </c>
       <c r="D50" t="n">
-        <v>125</v>
+        <v>62</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp3.150.000</t>
+          <t>Rp8.080.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp175.000</t>
+          <t>Rp150.000 - Rp350.000</t>
         </is>
       </c>
     </row>
@@ -8006,26 +8006,57 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
+          <t>Padre Padel Kelapa Gading</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>144</v>
+      </c>
+      <c r="D51" t="n">
+        <v>125</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>13.2%</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Rp3.150.000</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Rp125.000 - Rp175.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>wePADL at Meridian Sports &amp; Wellness (MSW) PIK</t>
         </is>
       </c>
-      <c r="C51" t="n">
+      <c r="C52" t="n">
         <v>90</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D52" t="n">
         <v>63</v>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>30.0%</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Rp6.500.000</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>Rp75.000 - Rp300.000</t>
         </is>
@@ -8126,16 +8157,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp1.110.000</t>
+          <t>Rp1.210.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8219,16 +8250,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp1.843.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8436,16 +8467,16 @@
         <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp250.000</t>
+          <t>Rp350.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8467,16 +8498,16 @@
         <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.300.000</t>
+          <t>Rp4.000.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8498,16 +8529,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.949.994</t>
+          <t>Rp3.074.994</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8560,16 +8591,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp495.000</t>
+          <t>Rp693.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8777,16 +8808,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp2.115.000</t>
+          <t>Rp2.475.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -9273,16 +9304,16 @@
         <v>64</v>
       </c>
       <c r="D40" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp294.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -9304,16 +9335,16 @@
         <v>72</v>
       </c>
       <c r="D41" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp1.175.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-12.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-12.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp720.000</t>
+          <t>Rp880.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp795.000</t>
+          <t>Rp894.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -606,16 +606,16 @@
         <v>34</v>
       </c>
       <c r="D6" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.300.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp8.550.500</t>
+          <t>Rp9.228.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -885,16 +885,16 @@
         <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.550.000</t>
+          <t>Rp3.950.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>112</v>
       </c>
       <c r="D16" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.168.000</t>
+          <t>Rp3.488.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -947,16 +947,16 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp3.100.000</t>
+          <t>Rp3.650.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>72</v>
       </c>
       <c r="D18" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp800.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.890.000</t>
+          <t>Rp2.920.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp750.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>136</v>
       </c>
       <c r="D22" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp10.825.000</t>
+          <t>Rp11.125.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp2.900.000</t>
+          <t>Rp3.450.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp5.950.000</t>
+          <t>Rp6.100.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp665.000</t>
+          <t>Rp540.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1319,16 +1319,16 @@
         <v>16</v>
       </c>
       <c r="D29" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp250.000</t>
+          <t>Rp500.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>85</v>
       </c>
       <c r="D33" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp1.494.000</t>
+          <t>Rp1.396.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp1.050.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp4.155.000</t>
+          <t>Rp4.345.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp7.700.000</t>
+          <t>Rp8.098.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1939,16 +1939,16 @@
         <v>26</v>
       </c>
       <c r="D49" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp115.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2001,16 +2001,16 @@
         <v>64</v>
       </c>
       <c r="D51" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp2.304.000</t>
+          <t>Rp2.880.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2063,16 +2063,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp640.000</t>
+          <t>Rp960.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>68</v>
       </c>
       <c r="D62" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp1.700.000</t>
+          <t>Rp2.060.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2528,16 +2528,16 @@
         <v>34</v>
       </c>
       <c r="D68" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp990.000</t>
+          <t>Rp1.089.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>102</v>
       </c>
       <c r="D70" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp6.975.000</t>
+          <t>Rp7.575.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>120</v>
       </c>
       <c r="D77" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp4.320.000</t>
+          <t>Rp3.960.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>108</v>
       </c>
       <c r="D78" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>54</v>
       </c>
       <c r="D81" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp297.000</t>
+          <t>Rp396.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3055,16 +3055,16 @@
         <v>96</v>
       </c>
       <c r="D85" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rp3.400.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3210,16 +3210,16 @@
         <v>119</v>
       </c>
       <c r="D90" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp3.540.000</t>
+          <t>Rp3.900.000</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp2.750.000</t>
+          <t>Rp3.150.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp405.000</t>
+          <t>Rp567.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3757,16 +3757,16 @@
         <v>32</v>
       </c>
       <c r="D8" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3788,16 +3788,16 @@
         <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.325.000</t>
+          <t>Rp2.525.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3819,16 +3819,16 @@
         <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp875.000</t>
+          <t>Rp973.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp2.500.000</t>
+          <t>Rp4.870.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp185.000</t>
+          <t>Rp370.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp400.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3974,16 +3974,16 @@
         <v>48</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.720.000</t>
+          <t>Rp1.880.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp2.143.000</t>
+          <t>Rp2.343.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -4346,16 +4346,16 @@
         <v>64</v>
       </c>
       <c r="D27" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp996.000</t>
+          <t>Rp2.490.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4718,16 +4718,16 @@
         <v>32</v>
       </c>
       <c r="D39" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4780,16 +4780,16 @@
         <v>52</v>
       </c>
       <c r="D41" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp3.499.000</t>
+          <t>Rp3.799.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>80</v>
       </c>
       <c r="D49" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp500.000</t>
+          <t>Rp850.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp5.300.000</t>
+          <t>Rp7.100.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp106.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5617,16 +5617,16 @@
         <v>84</v>
       </c>
       <c r="D68" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp8.510.000</t>
+          <t>Rp9.785.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5679,16 +5679,16 @@
         <v>30</v>
       </c>
       <c r="D70" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp1.875.000</t>
+          <t>Rp2.125.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5741,16 +5741,16 @@
         <v>162</v>
       </c>
       <c r="D72" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp1.100.000</t>
+          <t>Rp1.650.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5916,16 +5916,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp800.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp720.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp19.450.000</t>
+          <t>Rp20.650.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.900.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp1.450.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6257,16 +6257,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.165.000</t>
+          <t>Rp3.675.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp9.100.000</t>
+          <t>Rp9.200.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>101</v>
       </c>
       <c r="D3" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp2.650.000</t>
+          <t>Rp2.950.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>79</v>
       </c>
       <c r="D4" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp8.415.000</t>
+          <t>Rp8.975.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp11.260.500</t>
+          <t>Rp11.289.500</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp12.950.000</t>
+          <t>Rp13.375.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.475.000</t>
+          <t>Rp2.772.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp19.300.000</t>
+          <t>Rp19.900.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7176,21 +7176,21 @@
         <v>48</v>
       </c>
       <c r="D24" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp480.000</t>
+          <t>Rp740.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rp99.000 - Rp300.000</t>
+          <t>Rp99.000 - Rp260.000</t>
         </is>
       </c>
     </row>
@@ -7238,16 +7238,16 @@
         <v>36</v>
       </c>
       <c r="D26" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp100.000</t>
+          <t>Rp450.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>96</v>
       </c>
       <c r="D31" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.275.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>108</v>
       </c>
       <c r="D33" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp6.940.000</t>
+          <t>Rp6.010.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>187</v>
       </c>
       <c r="D34" t="n">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp10.350.000</t>
+          <t>Rp10.900.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>14</v>
       </c>
       <c r="D39" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp875.000</t>
+          <t>Rp1.225.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>150</v>
       </c>
       <c r="D40" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp22.825.000</t>
+          <t>Rp22.925.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>120</v>
       </c>
       <c r="D41" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp14.600.000</t>
+          <t>Rp19.000.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>102</v>
       </c>
       <c r="D46" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp860.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>36</v>
       </c>
       <c r="D47" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp5.790.000</t>
+          <t>Rp6.170.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -7920,16 +7920,16 @@
         <v>108</v>
       </c>
       <c r="D48" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp550.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -7951,16 +7951,16 @@
         <v>84</v>
       </c>
       <c r="D49" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp5.093.000</t>
+          <t>Rp5.791.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8126,16 +8126,16 @@
         <v>76</v>
       </c>
       <c r="D2" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp370.000</t>
+          <t>Rp740.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8157,16 +8157,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp1.210.000</t>
+          <t>Rp2.110.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.843.000</t>
+          <t>Rp4.235.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp370.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.180.000</t>
+          <t>Rp6.480.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp2.880.000</t>
+          <t>Rp3.310.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp12.780.000</t>
+          <t>Rp13.480.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>68</v>
       </c>
       <c r="D23" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp1.485.000</t>
+          <t>Rp2.115.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp2.475.000</t>
+          <t>Rp2.865.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8839,16 +8839,16 @@
         <v>36</v>
       </c>
       <c r="D25" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp668.000</t>
+          <t>Rp533.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp2.625.000</t>
+          <t>Rp2.375.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>54</v>
       </c>
       <c r="D28" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp2.550.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>32</v>
       </c>
       <c r="D31" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.350.000</t>
+          <t>Rp1.550.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>36</v>
       </c>
       <c r="D35" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp1.900.000</t>
+          <t>Rp2.095.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9273,16 +9273,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp4.325.000</t>
+          <t>Rp4.125.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -9304,16 +9304,16 @@
         <v>64</v>
       </c>
       <c r="D40" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp845.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-12.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-12.xlsx
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp894.000</t>
+          <t>Rp1.794.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -606,16 +606,16 @@
         <v>34</v>
       </c>
       <c r="D6" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.600.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -699,16 +699,16 @@
         <v>68</v>
       </c>
       <c r="D9" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp4.125.000</t>
+          <t>Rp5.625.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>69</v>
       </c>
       <c r="D10" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp3.531.992</t>
+          <t>Rp4.631.988</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp6.430.000</t>
+          <t>Rp6.760.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp9.228.500</t>
+          <t>Rp10.181.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -885,16 +885,16 @@
         <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.950.000</t>
+          <t>Rp4.550.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>72</v>
       </c>
       <c r="D18" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp800.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp3.450.000</t>
+          <t>Rp4.050.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp6.100.000</t>
+          <t>Rp7.700.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp3.250.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1319,16 +1319,16 @@
         <v>16</v>
       </c>
       <c r="D29" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp500.000</t>
+          <t>Rp876.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1350,16 +1350,16 @@
         <v>54</v>
       </c>
       <c r="D30" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp480.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>68</v>
       </c>
       <c r="D31" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.181.000</t>
+          <t>Rp2.460.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1412,16 +1412,16 @@
         <v>64</v>
       </c>
       <c r="D32" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp180.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.336.000</t>
+          <t>Rp2.730.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp1.050.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp4.345.000</t>
+          <t>Rp4.725.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>72</v>
       </c>
       <c r="D40" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp840.000</t>
+          <t>Rp1.680.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp780.000</t>
+          <t>Rp585.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp8.098.000</t>
+          <t>Rp10.548.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>198</v>
       </c>
       <c r="D44" t="n">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1908,16 +1908,16 @@
         <v>105</v>
       </c>
       <c r="D48" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp5.725.000</t>
+          <t>Rp6.075.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2001,16 +2001,16 @@
         <v>64</v>
       </c>
       <c r="D51" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp2.880.000</t>
+          <t>Rp3.456.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2032,16 +2032,16 @@
         <v>30</v>
       </c>
       <c r="D52" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp2.030.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2063,16 +2063,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp960.000</t>
+          <t>Rp1.040.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2125,16 +2125,16 @@
         <v>17</v>
       </c>
       <c r="D55" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp698.000</t>
+          <t>Rp898.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>32</v>
       </c>
       <c r="D58" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp1.125.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>80</v>
       </c>
       <c r="D60" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp720.000</t>
+          <t>Rp480.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>90</v>
       </c>
       <c r="D61" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp8.360.000</t>
+          <t>Rp8.460.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>68</v>
       </c>
       <c r="D62" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp2.060.000</t>
+          <t>Rp2.230.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2435,16 +2435,16 @@
         <v>36</v>
       </c>
       <c r="D65" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2466,16 +2466,16 @@
         <v>90</v>
       </c>
       <c r="D66" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp1.594.000</t>
+          <t>Rp3.190.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>102</v>
       </c>
       <c r="D70" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp7.575.000</t>
+          <t>Rp6.975.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>72</v>
       </c>
       <c r="D72" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp980.000</t>
+          <t>Rp1.320.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>98</v>
       </c>
       <c r="D75" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp1.680.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>45</v>
       </c>
       <c r="D76" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>108</v>
       </c>
       <c r="D78" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.800.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>126</v>
       </c>
       <c r="D80" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp2.982.000</t>
+          <t>Rp2.783.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>54</v>
       </c>
       <c r="D81" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp396.000</t>
+          <t>Rp595.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -2962,16 +2962,16 @@
         <v>36</v>
       </c>
       <c r="D82" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rp400.000</t>
+          <t>Rp528.000</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>138</v>
       </c>
       <c r="D88" t="n">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp5.450.000</t>
+          <t>Rp6.800.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3241,16 +3241,16 @@
         <v>36</v>
       </c>
       <c r="D91" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rp350.000</t>
+          <t>Rp525.000</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3303,16 +3303,16 @@
         <v>36</v>
       </c>
       <c r="D93" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rp596.000</t>
+          <t>Rp695.000</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3334,16 +3334,16 @@
         <v>34</v>
       </c>
       <c r="D94" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rp500.000</t>
+          <t>Rp725.000</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3365,16 +3365,16 @@
         <v>80</v>
       </c>
       <c r="D95" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rp3.631.000</t>
+          <t>Rp4.129.000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3393,24 +3393,24 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="D96" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp565.000</t>
+          <t>Rp1.445.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp220.000</t>
+          <t>Rp75.000 - Rp220.000</t>
         </is>
       </c>
     </row>
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp3.150.000</t>
+          <t>Rp3.390.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>127</v>
       </c>
       <c r="D3" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp15.246.500</t>
+          <t>Rp15.429.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>96</v>
       </c>
       <c r="D5" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp1.250.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3695,16 +3695,16 @@
         <v>68</v>
       </c>
       <c r="D6" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.050.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp370.000</t>
+          <t>Rp1.070.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp400.000</t>
+          <t>Rp500.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.750.000</t>
+          <t>Rp5.350.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4098,16 +4098,16 @@
         <v>36</v>
       </c>
       <c r="D19" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4470,16 +4470,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp800.000</t>
+          <t>Rp100.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rp130.000 - Rp250.000</t>
+          <t>Rp130.000 - Rp199.000</t>
         </is>
       </c>
     </row>
@@ -4625,16 +4625,16 @@
         <v>28</v>
       </c>
       <c r="D36" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp378.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4718,16 +4718,16 @@
         <v>32</v>
       </c>
       <c r="D39" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.050.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>80</v>
       </c>
       <c r="D49" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp850.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp106.000</t>
+          <t>Rp168.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5462,16 +5462,16 @@
         <v>64</v>
       </c>
       <c r="D63" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5524,16 +5524,16 @@
         <v>90</v>
       </c>
       <c r="D65" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp7.000.000</t>
+          <t>Rp6.600.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>102</v>
       </c>
       <c r="D66" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp891.000</t>
+          <t>Rp1.782.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5648,16 +5648,16 @@
         <v>144</v>
       </c>
       <c r="D69" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp4.050.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5741,16 +5741,16 @@
         <v>162</v>
       </c>
       <c r="D72" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp1.100.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5854,16 +5854,16 @@
         <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp300.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -5885,16 +5885,16 @@
         <v>333</v>
       </c>
       <c r="D3" t="n">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp15.125.000</t>
+          <t>Rp16.445.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5916,16 +5916,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp7.000.000</t>
+          <t>Rp8.000.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp720.000</t>
+          <t>Rp1.240.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp984.000</t>
+          <t>Rp1.634.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp1.450.000</t>
+          <t>Rp1.025.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp9.200.000</t>
+          <t>Rp9.600.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp11.705.000</t>
+          <t>Rp12.205.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp6.375.000</t>
+          <t>Rp9.175.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp11.289.500</t>
+          <t>Rp12.959.500</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp1.860.000</t>
+          <t>Rp2.260.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.833.000</t>
+          <t>Rp4.949.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp13.375.000</t>
+          <t>Rp13.925.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6897,16 +6897,16 @@
         <v>96</v>
       </c>
       <c r="D15" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6959,16 +6959,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp3.576.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.772.000</t>
+          <t>Rp2.970.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>60</v>
       </c>
       <c r="D20" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp693.000</t>
+          <t>Rp792.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp19.900.000</t>
+          <t>Rp20.600.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>72</v>
       </c>
       <c r="D22" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp9.475.000</t>
+          <t>Rp8.425.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -7145,21 +7145,21 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp3.529.000</t>
+          <t>Rp5.266.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rp81.000 - Rp175.000</t>
+          <t>Rp10.000 - Rp175.000</t>
         </is>
       </c>
     </row>
@@ -7207,16 +7207,16 @@
         <v>108</v>
       </c>
       <c r="D25" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp3.530.000</t>
+          <t>Rp4.530.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp6.150.000</t>
+          <t>Rp6.650.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>64</v>
       </c>
       <c r="D29" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp3.550.000</t>
+          <t>Rp3.990.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>96</v>
       </c>
       <c r="D30" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp3.903.000</t>
+          <t>Rp4.502.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>96</v>
       </c>
       <c r="D31" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.275.000</t>
+          <t>Rp1.225.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>108</v>
       </c>
       <c r="D33" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp6.010.000</t>
+          <t>Rp6.990.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>187</v>
       </c>
       <c r="D34" t="n">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp10.900.000</t>
+          <t>Rp12.650.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>67</v>
       </c>
       <c r="D35" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.520.000</t>
+          <t>Rp4.096.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>84</v>
       </c>
       <c r="D36" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp1.710.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>14</v>
       </c>
       <c r="D39" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp1.225.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>120</v>
       </c>
       <c r="D41" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp19.000.000</t>
+          <t>Rp19.800.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7796,16 +7796,16 @@
         <v>112</v>
       </c>
       <c r="D44" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp8.070.000</t>
+          <t>Rp8.455.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -8013,16 +8013,16 @@
         <v>144</v>
       </c>
       <c r="D51" t="n">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp3.150.000</t>
+          <t>Rp5.050.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -8126,16 +8126,16 @@
         <v>76</v>
       </c>
       <c r="D2" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp740.000</t>
+          <t>Rp1.110.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8157,16 +8157,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp2.110.000</t>
+          <t>Rp3.810.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.316.000</t>
+          <t>Rp1.836.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp4.235.000</t>
+          <t>Rp3.637.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.700.000</t>
+          <t>Rp2.525.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp370.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp1.220.000</t>
+          <t>Rp1.480.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.480.000</t>
+          <t>Rp6.885.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>108</v>
       </c>
       <c r="D11" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp660.000</t>
+          <t>Rp1.320.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8467,16 +8467,16 @@
         <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp350.000</t>
+          <t>Rp100.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.074.994</t>
+          <t>Rp4.124.990</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp693.000</t>
+          <t>Rp792.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp13.480.000</t>
+          <t>Rp14.920.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>68</v>
       </c>
       <c r="D23" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp2.115.000</t>
+          <t>Rp2.430.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp2.375.000</t>
+          <t>Rp3.374.995</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp4.140.000</t>
+          <t>Rp4.995.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>54</v>
       </c>
       <c r="D28" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>32</v>
       </c>
       <c r="D29" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp435.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp1.100.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>54</v>
       </c>
       <c r="D33" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp1.947.000</t>
+          <t>Rp2.292.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9180,16 +9180,16 @@
         <v>144</v>
       </c>
       <c r="D36" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp2.763.000</t>
+          <t>Rp2.565.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9211,16 +9211,16 @@
         <v>51</v>
       </c>
       <c r="D37" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp185.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9242,16 +9242,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp1.288.000</t>
+          <t>Rp1.387.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9304,16 +9304,16 @@
         <v>64</v>
       </c>
       <c r="D40" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp845.000</t>
+          <t>Rp676.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-12.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-12.xlsx
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp1.794.000</t>
+          <t>Rp1.944.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>69</v>
       </c>
       <c r="D10" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.631.988</t>
+          <t>Rp5.276.987</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp1.350.000</t>
+          <t>Rp1.650.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp3.250.000</t>
+          <t>Rp2.750.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp1.350.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>198</v>
       </c>
       <c r="D44" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp1.350.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>32</v>
       </c>
       <c r="D58" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp1.675.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>80</v>
       </c>
       <c r="D60" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp480.000</t>
+          <t>Rp720.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2497,16 +2497,16 @@
         <v>32</v>
       </c>
       <c r="D67" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp1.040.000</t>
+          <t>Rp520.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2714,16 +2714,16 @@
         <v>96</v>
       </c>
       <c r="D74" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rp4.700.000</t>
+          <t>Rp2.620.000</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>126</v>
       </c>
       <c r="D80" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp2.783.000</t>
+          <t>Rp3.081.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3334,16 +3334,16 @@
         <v>34</v>
       </c>
       <c r="D94" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rp725.000</t>
+          <t>Rp1.175.000</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp567.000</t>
+          <t>Rp729.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>96</v>
       </c>
       <c r="D5" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp1.250.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp1.070.000</t>
+          <t>Rp1.770.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp5.350.000</t>
+          <t>Rp5.950.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.050.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5471,12 +5471,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp4.700.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp500.000 - Rp600.000</t>
         </is>
       </c>
     </row>
@@ -5555,16 +5555,16 @@
         <v>102</v>
       </c>
       <c r="D66" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp1.782.000</t>
+          <t>Rp2.376.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp9.600.000</t>
+          <t>Rp9.760.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp4.949.000</t>
+          <t>Rp5.507.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6959,16 +6959,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp3.392.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>90</v>
       </c>
       <c r="D18" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp1.850.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.970.000</t>
+          <t>Rp3.069.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp20.600.000</t>
+          <t>Rp21.200.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>72</v>
       </c>
       <c r="D22" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp8.425.000</t>
+          <t>Rp7.725.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -7145,16 +7145,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp5.266.000</t>
+          <t>Rp5.441.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>96</v>
       </c>
       <c r="D31" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.225.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>187</v>
       </c>
       <c r="D34" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp12.650.000</t>
+          <t>Rp12.750.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>67</v>
       </c>
       <c r="D35" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp4.096.000</t>
+          <t>Rp4.760.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7796,16 +7796,16 @@
         <v>112</v>
       </c>
       <c r="D44" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp8.455.000</t>
+          <t>Rp8.565.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -8013,16 +8013,16 @@
         <v>144</v>
       </c>
       <c r="D51" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp5.050.000</t>
+          <t>Rp4.700.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -8157,16 +8157,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp3.810.000</t>
+          <t>Rp3.910.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8219,16 +8219,16 @@
         <v>86</v>
       </c>
       <c r="D5" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp5.190.000</t>
+          <t>Rp5.890.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp2.525.000</t>
+          <t>Rp2.250.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.885.000</t>
+          <t>Rp7.290.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp3.310.000</t>
+          <t>Rp3.740.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.124.990</t>
+          <t>Rp3.999.990</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp250.000</t>
+          <t>Rp650.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.050.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>17</v>
       </c>
       <c r="D22" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp320.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp2.865.000</t>
+          <t>Rp3.450.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>32</v>
       </c>
       <c r="D31" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.550.000</t>
+          <t>Rp1.850.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>54</v>
       </c>
       <c r="D33" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp2.292.000</t>
+          <t>Rp2.837.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9180,16 +9180,16 @@
         <v>144</v>
       </c>
       <c r="D36" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp2.565.000</t>
+          <t>Rp2.075.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9273,16 +9273,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp4.125.000</t>
+          <t>Rp2.425.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -9397,16 +9397,16 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp800.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-12.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-12.xlsx
@@ -730,16 +730,16 @@
         <v>69</v>
       </c>
       <c r="D10" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.276.987</t>
+          <t>Rp4.980.987</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp10.181.500</t>
+          <t>Rp10.681.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp7.700.000</t>
+          <t>Rp8.150.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.730.000</t>
+          <t>Rp2.926.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>54</v>
       </c>
       <c r="D81" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp595.000</t>
+          <t>Rp793.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3695,16 +3695,16 @@
         <v>68</v>
       </c>
       <c r="D6" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp1.770.000</t>
+          <t>Rp2.070.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6102,16 +6102,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp1.750.000</t>
+          <t>Rp1.250.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6587,16 +6587,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp199.000</t>
+          <t>Rp337.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.650.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>187</v>
       </c>
       <c r="D34" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp12.750.000</t>
+          <t>Rp12.900.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>120</v>
       </c>
       <c r="D41" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp19.800.000</t>
+          <t>Rp19.400.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp650.000</t>
+          <t>Rp950.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp3.374.995</t>
+          <t>Rp3.624.995</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>54</v>
       </c>
       <c r="D28" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp3.900.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -9273,16 +9273,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp2.425.000</t>
+          <t>Rp2.625.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
